--- a/assets/files/templates/SafePlum_work_plan.xlsx
+++ b/assets/files/templates/SafePlum_work_plan.xlsx
@@ -8403,12 +8403,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
@@ -8421,17 +8421,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
